--- a/data/WP18/WP18_sachgebiete_SPD_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_SPD_zeitreihe.xlsx
@@ -1775,13 +1775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A3DC76F-2708-4BFE-A425-827E19DE4BC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1B2278B-B88E-494C-8063-9F85A08EFCC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81041434-BF22-4EA1-8233-B31EBD67EAE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CDE5F33-DA53-4A16-B7C8-3B92DD5C9174}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82995D82-DB30-4F16-A02D-C92FFEA52067}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C3AA4F2-D32C-47D8-8F78-AC41D12AEF65}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_SPD_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_SPD_zeitreihe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">periode</t>
   </si>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Abgaben</t>
   </si>
   <si>
-    <t xml:space="preserve">Arbeit und Beschäftigung</t>
+    <t xml:space="preserve">Bauwesen</t>
   </si>
   <si>
     <t xml:space="preserve">Wohnungswesen</t>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t xml:space="preserve">Erneuerbare Energien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bauwesen</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G38" t="n">
         <v>6</v>
@@ -1775,13 +1772,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1B2278B-B88E-494C-8063-9F85A08EFCC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC9E1F47-5226-4012-BBAE-2CAEEACDFF6C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CDE5F33-DA53-4A16-B7C8-3B92DD5C9174}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECF93694-4F07-4612-9030-985A35AEC617}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C3AA4F2-D32C-47D8-8F78-AC41D12AEF65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE739951-ACD1-4EF9-9B61-4FC4209A8916}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_SPD_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_SPD_zeitreihe.xlsx
@@ -1772,13 +1772,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC9E1F47-5226-4012-BBAE-2CAEEACDFF6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E30F5075-0A38-4438-A537-882E639CB1B7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECF93694-4F07-4612-9030-985A35AEC617}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5532914-FEEA-4728-8EE6-EA8795BB3076}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE739951-ACD1-4EF9-9B61-4FC4209A8916}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A62AD062-4DAA-4533-9276-D0B91728470B}"/>
 </file>